--- a/outputs/tables/input_datasets.xlsx
+++ b/outputs/tables/input_datasets.xlsx
@@ -472,7 +472,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -570,7 +569,7 @@
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Overland ice-road centerlines (packed-snow tundra routes) burned into the overland network during the Jan-Apr season.</t>
+          <t>Overland ice-road centerlines (packed-snow tundra routes) burned into the overland network during the Jan-Mar season.</t>
         </is>
       </c>
     </row>
@@ -610,7 +609,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
@@ -671,7 +669,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Brown et al. 2026 (DOI 10.18739/A2SB3X15X), processed by gee_scripts/river_ice_full_pipeline.py</t>
+          <t>Brown et al. 2026 (DOI 10.18739/A2SB3X15X), processed by friction_preprocessing/river_ice_full_pipeline.py</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
